--- a/tests/fixtures/test_cases/mixed_realistic_lfs.xlsx
+++ b/tests/fixtures/test_cases/mixed_realistic_lfs.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="tbl1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="chart1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,163 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Employment by Sector</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!A1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$A$2:$A$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$B$2:$B$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'chart1'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'chart1'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'chart1'!$C$2:$C$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8640000" cy="4680000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -571,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,146 +427,68 @@
           <t>July 2026</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Population (thousands)</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32150.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>64.8</v>
+        <v>32000.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>Labour force</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19720.3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>34.7</v>
+        <v>21500.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unemployment</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1300.2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6</v>
+        <v>20100.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>confidential</t>
-        </is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1400.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Source: Statistics Canada, LFS, July 2026.</t>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Note: Seasonally adjusted.</t>
+          <t>Source: Statistics Canada, LFS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Goods</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B2" t="n">
-        <v>4420.8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15050.2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4475.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>15200.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Source: Statistics Canada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>x suppressed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/tests/fixtures/test_cases/mixed_realistic_lfs.xlsx
+++ b/tests/fixtures/test_cases/mixed_realistic_lfs.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="tbl1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="chart1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -122,6 +123,163 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Employment by Sector</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!A1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$A$2:$A$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$B$2:$B$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'chart1'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'chart1'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'chart1'!$C$2:$C$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,68 +585,146 @@
           <t>July 2026</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Population</t>
+          <t>Population (thousands)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32000.5</v>
+        <v>32150.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>64.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Labour force</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21500.8</v>
+        <v>19720.3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>34.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20100.3</v>
+        <v>1300.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unemployment</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1400.5</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>confidential</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Source: Statistics Canada, LFS, July 2026.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Source: Statistics Canada, LFS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Note: Seasonally adjusted.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4420.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15050.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4475.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15200.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Source: Statistics Canada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>x suppressed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>